--- a/animal_shelter_forms/008_pet_rescue_application_form--animal_shelter_forms.xlsx
+++ b/animal_shelter_forms/008_pet_rescue_application_form--animal_shelter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pet_type</t>
+          <t>pet_type_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pet Type</t>
+          <t>Pet Type 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pet_breed</t>
+          <t>pet_breed_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pet Breed</t>
+          <t>Pet Breed 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_goals</t>
+          <t>user_goals_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Why are you applying for a pet</t>
+          <t>User Goals 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pet_type_choices</t>
+          <t>pet_type_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pet_type_choices</t>
+          <t>pet_type_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pet_breed_choices</t>
+          <t>pet_breed_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pet_breed_choices</t>
+          <t>pet_breed_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
